--- a/templates/000_pm_suite/02_프로젝트 개발/04_설계/02_디자인설계/프로젝트명_저작권이미지사용서_V1.0_20230530.xlsx
+++ b/templates/000_pm_suite/02_프로젝트 개발/04_설계/02_디자인설계/프로젝트명_저작권이미지사용서_V1.0_20230530.xlsx
@@ -519,7 +519,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>[PM-41] SyncGuard AI UI/UX 디자인 에셋·폰트·아이콘 저작권 및 라이선스 관리대장 — 주식회사 한빛글로벌 SyncGuard AI 시스템 구축</t>
+          <t>[PM-41] SyncFlow AI UI/UX 디자인 에셋·폰트·아이콘 저작권 및 라이선스 관리대장 — 주식회사 한빛글로벌 SyncFlow AI 시스템 구축</t>
         </is>
       </c>
     </row>
@@ -585,7 +585,7 @@
       </c>
       <c r="C5" s="6" t="inlineStr">
         <is>
-          <t>한빛글로벌 CI 및 4대 브랜드 로고 에셋</t>
+          <t>한빛글로벌 CI 및 4대 사업본부 로고 에셋</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>SyncGuard AI 내 무제한 사용</t>
+          <t>SyncFlow AI 내 무제한 사용</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">
         <is>
-          <t>FO/BO 상단 GNB 헤더, PDF 심의리포트</t>
+          <t>FO/BO 상단 GNB 헤더, PDF 검증리포트</t>
         </is>
       </c>
       <c r="H5" s="6" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>네이버 / Microsoft</t>
+          <t>엔터프라이즈 / Microsoft</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
@@ -684,12 +684,12 @@
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>PDF 심의결과 리포트 생성 허용</t>
+          <t>PDF 검증결과 리포트 생성 허용</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>심의완료 증명서 PDF 다운로드 모듈</t>
+          <t>검증완료 증명서 PDF 다운로드 모듈</t>
         </is>
       </c>
       <c r="H7" s="6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>BO 심의 적발률 통계 및 FinOps 토큰 차트</t>
+          <t>BO 검증 적발률 통계 및 FinOps 토큰 차트</t>
         </is>
       </c>
       <c r="H9" s="6" t="inlineStr">
